--- a/backend/QuestionBank/Python.xlsx
+++ b/backend/QuestionBank/Python.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,753 @@
           <t>Tuples are immutable; list/dict/set are mutable.</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PY004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Loops</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Which loop is used to iterate over a sequence (list, tuple, string) in Python?</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>for</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>while</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>do-while</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>repeat</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>OptionA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>'for' iterates directly over the items of a sequence.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PY005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Data Types</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>What is the correct way to create an empty list in Python?</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>list()</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>OptionB</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>[] and list() both create an empty list, but [] is the standard literal form asked here.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PY006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Strings</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CodeCompletion</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Complete the code so it prints the length of the string 'hello':
+s = 'hello'
+print(___(s))</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>len</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>len() returns the number of characters in a string.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PY007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Exception Handling</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Which block always executes, whether or not an exception occurred?</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>try</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>except</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>finally</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>else</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>OptionC</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>'finally' runs regardless of whether an exception was raised.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PY008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dictionaries</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Which method safely retrieves a value from a dictionary without raising a KeyError if the key is missing?</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>dict[key]</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>dict.get(key)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>dict.fetch(key)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dict.find(key)</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>OptionB</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>dict.get(key) returns None (or a default) instead of raising KeyError.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PY009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Functions</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CodeCompletion</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Complete the function so it returns the square of n:
+def square(n):
+    return n ___ 2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>The ** operator raises n to the given power; n ** 2 squares n.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PY010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>List Comprehension</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CodeCompletion</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Complete the list comprehension so squares holds the square of every number from 0 to 4:
+squares = [x**2 for x in ___(5)]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>range(5) produces 0,1,2,3,4, so the comprehension squares each of them.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PY011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Decorators</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>What does a Python decorator primarily do?</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Wraps a function to extend its behavior without modifying its code</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Deletes a function after it runs once</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Converts a function into a class</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Compiles Python code to bytecode ahead of time</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>OptionA</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>A decorator takes a function and returns a new function that adds behavior around it.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PY012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Generators</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>What keyword turns a function into a generator?</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>return</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>yield</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>async</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>generate</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>OptionB</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>'yield' pauses the function and produces a value, making it a generator.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PY013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Because of the GIL (Global Interpreter Lock), what is true about CPython threads?</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Only one thread executes Python bytecode at a time, so threads don't speed up CPU-bound work</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Threads run fully in parallel on multiple cores for any workload</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>The GIL only affects I/O-bound code, never CPU-bound code</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Python has no GIL when using the threading module</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>OptionA</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>The GIL lets only one thread run Python bytecode at a time, so threading helps I/O-bound, not CPU-bound, work.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PY014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>OOP</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>What is method resolution order (MRO) used for in Python?</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Determining the order in which base classes are searched when resolving an attribute/method</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sorting methods alphabetically within a class</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Deciding the order methods are called in a for loop</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Compiling methods into bytecode</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>OptionA</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MRO defines the order Python searches parent classes for an attribute or method, relevant with multiple inheritance.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PY015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Context Managers</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CodeCompletion</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Complete the code so the file is automatically closed after the block, using a context manager:
+___ open('data.txt') as f:
+    data = f.read()</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>with</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>The 'with' statement is a context manager; it closes the file automatically on exit.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
